--- a/Boom Arm Electrode Holder/BOM - Boom arm stand.xlsx
+++ b/Boom Arm Electrode Holder/BOM - Boom arm stand.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jamesryan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jamesryan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF38671C-8CCA-9547-BD8C-245C9BFCB2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B34EC2-8323-7A43-82C1-E438DFB0A3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="880" windowWidth="28040" windowHeight="17180" xr2:uid="{ACE7327C-E6AB-794C-A207-722F13B84BF1}"/>
+    <workbookView xWindow="2200" yWindow="2420" windowWidth="28040" windowHeight="17180" xr2:uid="{ACE7327C-E6AB-794C-A207-722F13B84BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Qty</t>
   </si>
@@ -86,9 +86,6 @@
     <t>https://www.harborfreight.com/multi-position-magnetic-base-with-fine-adjustment-63663.html</t>
   </si>
   <si>
-    <t>Total cost</t>
-  </si>
-  <si>
     <t>1 set</t>
   </si>
   <si>
@@ -102,6 +99,33 @@
   </si>
   <si>
     <t>varies</t>
+  </si>
+  <si>
+    <t>20ga dispensing needle</t>
+  </si>
+  <si>
+    <t>stereo audio female jack with wire</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B082VVWND3?ref=ppx_yo2ov_dt_b_fed_asin_title</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B07QQ59JL6?ref=ppx_yo2ov_dt_b_fed_asin_title&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B07P2H6KR5?ref=ppx_yo2ov_dt_b_fed_asin_title&amp;th=1</t>
+  </si>
+  <si>
+    <t>6 inch coated copper magnet wire 28ga</t>
+  </si>
+  <si>
+    <t>6 inch bare copper wire 24 ga</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/HWYEE-24Gauge-electroculture-Gardening-187FT/dp/B0F5Q8WBFD/ref=sr_1_5?crid=21N1Q6JXZYOUV&amp;dib=eyJ2IjoiMSJ9.k50617LNUKbr3n2VevIq1E5A7OuEJVis3T7hctqAKN2fdmjqm3PUvr7k9z79va7P5XMDcw6lhXiBB0Wloi5TGxU07yzRx8o1ULhRX69KCKOo8oUSYvdUIQfQUWqRpd</t>
+  </si>
+  <si>
+    <t>You only need about 6 inches</t>
   </si>
 </sst>
 </file>
@@ -187,12 +211,6 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -200,6 +218,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -537,42 +561,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E3686D-EE5C-C649-A0F8-89871342D151}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="10.83203125" style="5"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="38.5" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -580,17 +604,17 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>19.59</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <f>A3*B3</f>
         <v>39.18</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
@@ -601,17 +625,17 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>17.5</v>
       </c>
-      <c r="C4" s="5">
-        <f t="shared" ref="C4:C11" si="0">A4*B4</f>
+      <c r="C4" s="3">
+        <f t="shared" ref="C4:C5" si="0">A4*B4</f>
         <v>17.5</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
@@ -622,17 +646,17 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>12.99</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <f t="shared" si="0"/>
         <v>12.99</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
@@ -640,45 +664,107 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="C9">
+        <v>0.35</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="7">
-        <f>C3+C5+3</f>
-        <v>55.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C9"/>
+      <c r="E9" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C10"/>
+      <c r="A10" s="6">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11"/>
       <c r="C11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12"/>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13"/>
+      <c r="C13" s="5">
+        <f>SUM(C3:C5)+SUM(C7:C10)</f>
+        <v>71.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14"/>
+      <c r="C14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -689,6 +775,8 @@
     <hyperlink ref="E4" r:id="rId2" xr:uid="{55DB2AB2-EB39-F042-824A-33D2838BD0EC}"/>
     <hyperlink ref="E5" r:id="rId3" xr:uid="{2CCB92D9-2390-5E44-A417-67FB0F4A805A}"/>
     <hyperlink ref="E6" r:id="rId4" xr:uid="{F8BB8FE8-B237-1C4E-88AA-2F9A7933E7D3}"/>
+    <hyperlink ref="E10" r:id="rId5" xr:uid="{52782073-C92E-8E4B-9AFA-404B42559BAE}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{B2669D81-89C8-DA47-B653-7E63F5F7BC59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
